--- a/backups/room-checkout-2026-09-15.xlsx
+++ b/backups/room-checkout-2026-09-15.xlsx
@@ -20191,7 +20191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:30 UTC</t>
+          <t>2026-09-15 21:31 UTC</t>
         </is>
       </c>
     </row>

--- a/backups/room-checkout-2026-09-15.xlsx
+++ b/backups/room-checkout-2026-09-15.xlsx
@@ -20191,7 +20191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:31 UTC</t>
+          <t>2026-09-15 21:32 UTC</t>
         </is>
       </c>
     </row>
